--- a/SocialPerks_Restaurants_Vienna.xlsx
+++ b/SocialPerks_Restaurants_Vienna.xlsx
@@ -4939,7 +4939,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>27/06/2026 11:56</t>
+          <t>28/06/2026 18:39</t>
         </is>
       </c>
     </row>
